--- a/output/pdf_financials_xlsx/CVO.xlsx
+++ b/output/pdf_financials_xlsx/CVO.xlsx
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.203</v>
+        <v>3.788</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3.467</v>
+        <v>7.661</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>4.126</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>3.959</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>4.039</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>3.988</v>
       </c>
     </row>
     <row r="29">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-488.655</v>
+        <v>-485.07</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>232.774</v>
+        <v>236.968</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-39.527</v>
+        <v>-35.401</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-23.346</v>
+        <v>-19.387</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-15.331</v>
+        <v>-11.292</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-27.117</v>
+        <v>-23.129</v>
       </c>
     </row>
     <row r="30">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-753.4344789305703</v>
+        <v>-747.9069337157131</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>269.140227546018</v>
+        <v>273.9894551845343</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-35.29133408331994</v>
+        <v>-31.60747129515544</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-18.5147588307136</v>
+        <v>-15.37503767030945</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-11.50354162914941</v>
+        <v>-8.472897532865117</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-18.28042524218176</v>
+        <v>-15.59198862065944</v>
       </c>
     </row>
     <row r="31">
@@ -2939,22 +2939,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>3.788</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>7.661</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>4.126</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>3.959</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>4.039</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>3.988</v>
       </c>
     </row>
     <row r="101">
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -6274,7 +6274,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6354,7 +6358,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -6690,7 +6698,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7694,7 +7706,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>2.008</v>
       </c>
@@ -7740,7 +7756,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -7786,7 +7802,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>1.577</v>
       </c>
@@ -8374,7 +8394,11 @@
           <t>Proceeds from disposal of property and equipment 8</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.004</v>
       </c>
@@ -8420,7 +8444,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>-0.499</v>
       </c>
@@ -9372,7 +9400,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -9452,7 +9484,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10640,7 +10676,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>2.008</v>
       </c>
@@ -10686,7 +10726,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -10732,7 +10772,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>1.577</v>
       </c>

--- a/output/pdf_financials_xlsx/CVO.xlsx
+++ b/output/pdf_financials_xlsx/CVO.xlsx
@@ -2037,22 +2037,22 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.534</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>2.889</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="65">
@@ -2137,22 +2137,22 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>16.55</v>
+        <v>18.34</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>22.91</v>
+        <v>25.444</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>21.435</v>
+        <v>24.505</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>21.822</v>
+        <v>24.711</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.602</v>
+        <v>18.915</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>19.688</v>
+        <v>20.295</v>
       </c>
     </row>
     <row r="69">
@@ -2187,22 +2187,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>1.555</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>1.916</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>1.929</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>2.153</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>1.999</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="71">
@@ -2212,22 +2212,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>1.555</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>1.916</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>1.929</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>2.153</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>1.999</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="72">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>38.019</v>
+        <v>34.674</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>51.282</v>
+        <v>46.832</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.999</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>12.588</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>11.169</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>8.94</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>6.885</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>5.464</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="79">
@@ -2416,22 +2416,22 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>12.588</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>11.169</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>8.94</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>6.885</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>5.464</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="80">
@@ -2440,35 +2440,23 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>-0.01415603771073158</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.05122613883712554</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.0497361954487423</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.05062652991491293</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.05880684280614939</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.1656953987996869</v>
       </c>
     </row>
     <row r="81">
@@ -2578,10 +2566,10 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>951.622</v>
+        <v>939.034</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>11.682</v>
+        <v>0.513</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>0</v>
@@ -2590,10 +2578,10 @@
         <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>5.464</v>
+        <v>0</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>13.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4528,7 +4516,11 @@
           <t>Current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4612,7 +4604,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5530,7 +5526,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>1.555</v>
       </c>
@@ -5622,7 +5622,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>12.588</v>
       </c>
@@ -6486,7 +6490,11 @@
           <t>Deferred income tax expense (recovery) 20</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -7300,7 +7308,11 @@
           <t>Deferred income tax recovery 20</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -7618,7 +7630,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>-600.025</v>
       </c>
